--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2706,10 +2706,8 @@
           <t>2026-07-17 10:59:57</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>561380</t>
-        </is>
+      <c r="B32" t="n">
+        <v>561380</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2774,6 +2772,156 @@
       </c>
       <c r="V32" t="n">
         <v>-2960</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-17 14:45:01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>561380</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-12.51580278128952</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-19.2532088681447</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-26.14727854855924</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-29.17093142272262</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-29.17093142272262</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-29.17093142272262</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-14.77832512315272</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>本地日线缓存(data\cache\561380_daily.json) + AKShare fund_etf_spot_em(EastMoney) + AKShare fund_etf_hist_min_em(15m)</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-14.78</v>
+      </c>
+      <c r="V33" t="n">
+        <v>-295.57</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-17 14:55:01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>561380</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-13.02149178255374</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-19.71995332555426</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-26.57417289220919</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-29.58034800409417</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-29.58034800409417</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-29.58034800409417</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-15.27093596059115</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>本地日线缓存(data\cache\561380_daily.json) + AKShare fund_etf_spot_em(EastMoney) + AKShare fund_etf_hist_min_em(5m)</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-15.27</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-305.42</v>
       </c>
     </row>
   </sheetData>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2854,10 +2854,8 @@
           <t>2026-07-17 14:55:01</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>561380</t>
-        </is>
+      <c r="B34" t="n">
+        <v>561380</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2921,6 +2919,82 @@
         <v>-15.27</v>
       </c>
       <c r="V34" t="n">
+        <v>-305.42</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:16:43</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>561380</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-13.02149178255374</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-19.71995332555426</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-26.57417289220919</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-29.58034800409417</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-29.58034800409417</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-29.58034800409417</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-15.27093596059115</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>AKShare历史日线(EastMoney)</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-15.27</v>
+      </c>
+      <c r="V35" t="n">
         <v>-305.42</v>
       </c>
     </row>

--- a/data/history.xlsx
+++ b/data/history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2928,10 +2928,8 @@
           <t>2026-07-17 15:16:43</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>561380</t>
-        </is>
+      <c r="B35" t="n">
+        <v>561380</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2996,6 +2994,82 @@
       </c>
       <c r="V35" t="n">
         <v>-305.42</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:21:12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>561380</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>电网设备ETF</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-3.212851405622497</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-9.511889862327916</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-15.04112808460635</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-68.70129870129871</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-70.3931203931204</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-70.3931203931204</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-70.3931203931204</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-10.96059113300494</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>AKShare历史日线(Sina)</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-10.96</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-219.21</v>
       </c>
     </row>
   </sheetData>
